--- a/output/stock_quant_scores/NVDA_balance_df.xlsx
+++ b/output/stock_quant_scores/NVDA_balance_df.xlsx
@@ -1842,27 +1842,37 @@
       <c r="E6" t="n">
         <v>6116000000</v>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>11831000000</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>24494000000</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>26612000000</v>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>10756000000</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>16235000000</v>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>17575000000</v>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -1875,7 +1885,9 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>4335000000</v>
+      </c>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
@@ -1896,7 +1908,9 @@
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>44187000000</v>
+      </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
@@ -1924,12 +1938,16 @@
       <c r="BS6" t="inlineStr"/>
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
+      <c r="BV6" t="n">
+        <v>28829000000</v>
+      </c>
       <c r="BW6" t="inlineStr"/>
       <c r="BX6" t="n">
         <v>239000000</v>
       </c>
-      <c r="BY6" t="inlineStr"/>
+      <c r="BY6" t="n">
+        <v>2605000000</v>
+      </c>
       <c r="BZ6" t="inlineStr"/>
       <c r="CA6" t="inlineStr"/>
       <c r="CB6" t="inlineStr"/>
@@ -1943,7 +1961,9 @@
       </c>
       <c r="CG6" t="inlineStr"/>
       <c r="CH6" t="inlineStr"/>
-      <c r="CI6" t="inlineStr"/>
+      <c r="CI6" t="n">
+        <v>1990000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
